--- a/templates/PORTFOLIO FIDC - template.xlsx
+++ b/templates/PORTFOLIO FIDC - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1405,96 +1405,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1194.31802471289</v>
+        <v>1210.36095135846</v>
       </c>
       <c r="D17" s="37" t="n">
-        <v>0.000846919063347551</v>
+        <v>0.0009608413842201458</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>1.560674050740996</v>
+        <v>1.77060628356061</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>1193.30738993592</v>
+        <v>1209.19910281871</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>-0.001407746432663948</v>
+        <v>-6.794468538340315e-05</v>
       </c>
       <c r="E18" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>-2.594147921051378</v>
+        <v>-0.1252061878788089</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>1194.9896323279</v>
+        <v>1209.28126705394</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>-0.0001812472459098435</v>
+        <v>0.0005984079600844794</v>
       </c>
       <c r="E19" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>-0.3339963471145579</v>
+        <v>1.102726122811864</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>1195.20626017085</v>
+        <v>1208.55805629283</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.001398276158552036</v>
+        <v>0.001132296633020724</v>
       </c>
       <c r="E20" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2.5766964174786</v>
+        <v>2.086558266750997</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>1193.53736532857</v>
+        <v>1207.19115780943</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>4.098018708620366e-05</v>
+        <v>0.001440279163900549</v>
       </c>
       <c r="E21" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>0.07551691460002399</v>
+        <v>2.654098147274894</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1534,18 +1534,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr"/>
       <c r="D24" s="37" t="n">
-        <v>0.008218008182438785</v>
+        <v>0.01087617150561448</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>0.7839091980064949</v>
+        <v>2.858519890609255</v>
       </c>
       <c r="G24" s="44" t="n"/>
     </row>
@@ -1558,13 +1558,13 @@
       </c>
       <c r="C25" s="46" t="inlineStr"/>
       <c r="D25" s="41" t="n">
-        <v>0.01523234296624665</v>
+        <v>0.01705616414535638</v>
       </c>
       <c r="E25" s="41" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>1.313375868553745</v>
+        <v>1.481801959036811</v>
       </c>
       <c r="G25" s="47" t="n"/>
       <c r="H25" s="48" t="n"/>
@@ -1578,13 +1578,13 @@
       </c>
       <c r="C26" s="46" t="inlineStr"/>
       <c r="D26" s="41" t="n">
-        <v>0.03463677078604022</v>
+        <v>0.04483742704766636</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>0.9815414748631782</v>
+        <v>1.273839180636536</v>
       </c>
       <c r="G26" s="47" t="n"/>
     </row>
@@ -1597,13 +1597,13 @@
       </c>
       <c r="C27" s="46" t="inlineStr"/>
       <c r="D27" s="41" t="n">
-        <v>0.1073709452464717</v>
+        <v>0.1045153505312195</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>1.494005231209007</v>
+        <v>1.456148358588038</v>
       </c>
       <c r="G27" s="47" t="n"/>
     </row>
@@ -1616,13 +1616,13 @@
       </c>
       <c r="C28" s="46" t="inlineStr"/>
       <c r="D28" s="41" t="n">
-        <v>0.03083850482487849</v>
+        <v>0.04468545862959061</v>
       </c>
       <c r="E28" s="41" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F28" s="42" t="n">
-        <v>0.9506606601978518</v>
+        <v>1.174221716133214</v>
       </c>
       <c r="G28" s="47" t="n"/>
     </row>
@@ -1654,13 +1654,13 @@
       </c>
       <c r="C30" s="46" t="inlineStr"/>
       <c r="D30" s="41" t="n">
-        <v>0.1943180247128902</v>
+        <v>0.2103609513584599</v>
       </c>
       <c r="E30" s="41" t="n">
-        <v>0.1176426567269842</v>
+        <v>0.1237225148716596</v>
       </c>
       <c r="F30" s="42" t="n">
-        <v>1.651765015506647</v>
+        <v>1.700264107763024</v>
       </c>
       <c r="G30" s="47" t="n"/>
     </row>
@@ -1691,7 +1691,7 @@
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="52" t="n">
-        <v>77172222.6015</v>
+        <v>78208854.61939999</v>
       </c>
       <c r="F33" s="29" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1706,7 +1706,7 @@
       <c r="C34" s="14" t="n"/>
       <c r="D34" s="14" t="n"/>
       <c r="E34" s="52" t="n">
-        <v>43442884.97351034</v>
+        <v>45055806.10369718</v>
       </c>
       <c r="F34" s="29" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D36" s="20" t="n"/>
